--- a/informes_data/Primera FEB/2025-26/playoffs/individual/NP_play_by_play_2513267_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/playoffs/individual/NP_play_by_play_2513267_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.5928</v>
+        <v>3.6293</v>
       </c>
       <c r="E2" t="n">
-        <v>4.6362</v>
+        <v>3.5287</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0435</v>
+        <v>0.1006</v>
       </c>
       <c r="G2" t="n">
         <v>-0.7648</v>
@@ -610,13 +610,13 @@
         <v>2.8635</v>
       </c>
       <c r="S2" t="n">
-        <v>2.6799</v>
+        <v>1.7164</v>
       </c>
       <c r="T2" t="n">
-        <v>2.4119</v>
+        <v>1.3043</v>
       </c>
       <c r="U2" t="n">
-        <v>0.268</v>
+        <v>0.4121</v>
       </c>
       <c r="V2" t="n">
         <v>-0.1859</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. ANSORREGUI DEBA</t>
+          <t>G. KORSANTIA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3128</v>
+        <v>2.7498</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.2982</v>
+        <v>1.981</v>
       </c>
       <c r="F3" t="n">
-        <v>3.6109</v>
+        <v>0.7688</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.1038</v>
+        <v>0.4757</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.3484</v>
+        <v>0.1286</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.7554</v>
+        <v>0.347</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.4668</v>
+        <v>1.1799</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0194</v>
+        <v>0.4964</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.4862</v>
+        <v>0.6835</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.637</v>
+        <v>-0.7043</v>
       </c>
       <c r="N3" t="n">
         <v>-0.3678</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2692</v>
+        <v>-0.3365</v>
       </c>
       <c r="P3" t="n">
-        <v>2.423</v>
+        <v>1.9825</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.423</v>
+        <v>1.9825</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4957</v>
+        <v>0.667</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1686</v>
+        <v>0.4311</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3271</v>
+        <v>0.236</v>
       </c>
       <c r="V3" t="n">
-        <v>1.4979</v>
+        <v>-0.3754</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.37</v>
       </c>
       <c r="X3" t="n">
-        <v>1.4979</v>
+        <v>-0.7453</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. KORSANTIA</t>
+          <t>M. ANSORREGUI DEBA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2849</v>
+        <v>2.1815</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7467</v>
+        <v>-1.17</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5382</v>
+        <v>3.3515</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4757</v>
+        <v>-2.1038</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1286</v>
+        <v>-0.3484</v>
       </c>
       <c r="I4" t="n">
-        <v>0.347</v>
+        <v>-1.7554</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1799</v>
+        <v>-1.4668</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4964</v>
+        <v>0.0194</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6835</v>
+        <v>-1.4862</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.7043</v>
+        <v>-0.637</v>
       </c>
       <c r="N4" t="n">
         <v>-0.3678</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3365</v>
+        <v>-0.2692</v>
       </c>
       <c r="P4" t="n">
-        <v>1.9825</v>
+        <v>2.423</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.9825</v>
+        <v>2.423</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2021</v>
+        <v>0.3644</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1967</v>
+        <v>0.2967</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0054</v>
+        <v>0.0677</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.3754</v>
+        <v>1.4979</v>
       </c>
       <c r="W4" t="n">
-        <v>0.37</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.7453</v>
+        <v>1.4979</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. NGOM</t>
+          <t>A. ZUBIZARRETA ARANBARRI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7639</v>
+        <v>0.8542</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.9155</v>
+        <v>-0.0148</v>
       </c>
       <c r="F5" t="n">
-        <v>2.6794</v>
+        <v>0.869</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8733</v>
+        <v>-0.4924</v>
       </c>
       <c r="H5" t="n">
-        <v>0.918</v>
+        <v>-1.1433</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0447</v>
+        <v>0.6508</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9781</v>
+        <v>-0.2619</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8642</v>
+        <v>-0.8695000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1139</v>
+        <v>0.6076</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1048</v>
+        <v>-0.2305</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0538</v>
+        <v>-0.2738</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1586</v>
+        <v>0.0433</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.3216</v>
+        <v>-0.2203</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.3041</v>
+        <v>-1.1014</v>
       </c>
       <c r="R5" t="n">
-        <v>1.9825</v>
+        <v>0.8811</v>
       </c>
       <c r="S5" t="n">
-        <v>2.5831</v>
+        <v>0.6339</v>
       </c>
       <c r="T5" t="n">
-        <v>1.4105</v>
+        <v>0.2296</v>
       </c>
       <c r="U5" t="n">
-        <v>1.1726</v>
+        <v>0.4043</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3709</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.1189</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3709</v>
+        <v>-0.1859</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. NICOLAU ALEDON</t>
+          <t>A. NGOM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5535</v>
+        <v>0.6395</v>
       </c>
       <c r="E6" t="n">
-        <v>1.4112</v>
+        <v>-1.6075</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8577</v>
+        <v>2.247</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.6181</v>
+        <v>0.8733</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.247</v>
+        <v>0.918</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3711</v>
+        <v>-0.0447</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.3816</v>
+        <v>0.9781</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.4576</v>
+        <v>0.8642</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0759</v>
+        <v>0.1139</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.2365</v>
+        <v>-0.1048</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7894</v>
+        <v>0.0538</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.447</v>
+        <v>-0.1586</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1014</v>
+        <v>-1.3216</v>
       </c>
       <c r="Q6" t="n">
+        <v>-3.3041</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.9825</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.4587</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.7185</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.7402</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-0.3709</v>
+      </c>
+      <c r="W6" t="n">
         <v>0</v>
       </c>
-      <c r="R6" t="n">
-        <v>1.1014</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.3213</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0.4889</v>
-      </c>
-      <c r="U6" t="n">
-        <v>-0.1676</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0.7489</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.3039</v>
-      </c>
       <c r="X6" t="n">
-        <v>-0.555</v>
+        <v>-0.3709</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. ZUBIZARRETA ARANBARRI</t>
+          <t>J. NICOLAU ALEDON</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0602</v>
+        <v>0.2904</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6647</v>
+        <v>1.1769</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7248</v>
+        <v>-0.8865</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4924</v>
+        <v>-1.6181</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.1433</v>
+        <v>-1.247</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6508</v>
+        <v>-0.3711</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.2619</v>
+        <v>-0.3816</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.8695000000000001</v>
+        <v>-0.4576</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6076</v>
+        <v>0.0759</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2305</v>
+        <v>-1.2365</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2738</v>
+        <v>-0.7894</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0433</v>
+        <v>-0.447</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.2203</v>
+        <v>1.1014</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1014</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.8811</v>
+        <v>1.1014</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1601</v>
+        <v>0.0582</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4203</v>
+        <v>0.2546</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2601</v>
+        <v>-0.1964</v>
       </c>
       <c r="V7" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.7489</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1189</v>
+        <v>1.3039</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1859</v>
+        <v>-0.555</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0172</v>
+        <v>-0.6983</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0625</v>
+        <v>0.0547</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.9547</v>
+        <v>-0.753</v>
       </c>
       <c r="G8" t="n">
         <v>0.5646</v>
@@ -1078,13 +1078,13 @@
         <v>1.5419</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7185</v>
+        <v>-0.3995</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3843</v>
+        <v>-0.2672</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3341</v>
+        <v>-0.1324</v>
       </c>
       <c r="V8" t="n">
         <v>-1.3039</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. MAIZA APECECHEA</t>
+          <t>J. TATE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9841</v>
+        <v>-1.2024</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.5762</v>
+        <v>-3.4421</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.4079</v>
+        <v>2.2397</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.6349</v>
+        <v>-0.4554</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.0023</v>
+        <v>1.6038</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6326000000000001</v>
+        <v>-2.0592</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.4016</v>
+        <v>-0.0331</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.4396</v>
+        <v>1.8002</v>
       </c>
       <c r="L9" t="n">
-        <v>0.038</v>
+        <v>-1.8333</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.2332</v>
+        <v>-0.4224</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5627</v>
+        <v>-0.1964</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6705</v>
+        <v>-0.2259</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.6608000000000001</v>
+        <v>-2.6433</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1014</v>
+        <v>-5.5068</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4405</v>
+        <v>2.8635</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6224</v>
+        <v>0.7827</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1922</v>
+        <v>0.2389</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4302</v>
+        <v>0.5438</v>
       </c>
       <c r="V9" t="n">
-        <v>0.9339</v>
+        <v>1.1135</v>
       </c>
       <c r="W9" t="n">
-        <v>1.1189</v>
+        <v>1.8589</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.185</v>
+        <v>-0.7453</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. TATE</t>
+          <t>G. MAIZA APECECHEA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.041</v>
+        <v>-1.9265</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.7418</v>
+        <v>-0.5762</v>
       </c>
       <c r="F10" t="n">
-        <v>2.7009</v>
+        <v>-1.3502</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.4554</v>
+        <v>-1.6349</v>
       </c>
       <c r="H10" t="n">
-        <v>1.6038</v>
+        <v>-1.0023</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.0592</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.0331</v>
+        <v>-0.4016</v>
       </c>
       <c r="K10" t="n">
-        <v>1.8002</v>
+        <v>-0.4396</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.8333</v>
+        <v>0.038</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4224</v>
+        <v>-1.2332</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1964</v>
+        <v>-0.5627</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2259</v>
+        <v>-0.6705</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.6433</v>
+        <v>-0.6608000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>-5.5068</v>
+        <v>-1.1014</v>
       </c>
       <c r="R10" t="n">
-        <v>2.8635</v>
+        <v>0.4405</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0558</v>
+        <v>-0.5647</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0608</v>
+        <v>-0.1922</v>
       </c>
       <c r="U10" t="n">
-        <v>1.005</v>
+        <v>-0.3726</v>
       </c>
       <c r="V10" t="n">
-        <v>1.1135</v>
+        <v>0.9339</v>
       </c>
       <c r="W10" t="n">
-        <v>1.8589</v>
+        <v>1.1189</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.7453</v>
+        <v>-0.185</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.9276</v>
+        <v>-7.2788</v>
       </c>
       <c r="E11" t="n">
-        <v>-7.6965</v>
+        <v>-7.4512</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2312</v>
+        <v>0.1724</v>
       </c>
       <c r="G11" t="n">
         <v>-5.328</v>
@@ -1312,13 +1312,13 @@
         <v>2.6433</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8199</v>
+        <v>-0.1711</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1516</v>
+        <v>0.0936</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6683</v>
+        <v>-0.2647</v>
       </c>
       <c r="V11" t="n">
         <v>-1.1189</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.4018</v>
+        <v>-0.7613000000000012</v>
       </c>
       <c r="E12" t="n">
-        <v>-8.161300000000001</v>
+        <v>-7.520499999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>6.7592</v>
+        <v>6.7593</v>
       </c>
       <c r="G12" t="n">
         <v>-10.4838</v>
@@ -1363,16 +1363,16 @@
         <v>-8.3758</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.7774</v>
+        <v>-3.777400000000001</v>
       </c>
       <c r="K12" t="n">
         <v>1.5699</v>
       </c>
       <c r="L12" t="n">
-        <v>-5.347399999999999</v>
+        <v>-5.3474</v>
       </c>
       <c r="M12" t="n">
-        <v>-6.7063</v>
+        <v>-6.706300000000001</v>
       </c>
       <c r="N12" t="n">
         <v>-3.678</v>
@@ -1390,10 +1390,10 @@
         <v>18.7232</v>
       </c>
       <c r="S12" t="n">
-        <v>3.905400000000001</v>
+        <v>4.546</v>
       </c>
       <c r="T12" t="n">
-        <v>2.4674</v>
+        <v>3.1079</v>
       </c>
       <c r="U12" t="n">
         <v>1.438</v>
@@ -1405,7 +1405,7 @@
         <v>8.5679</v>
       </c>
       <c r="X12" t="n">
-        <v>-6.695500000000001</v>
+        <v>-6.6955</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.4161</v>
+        <v>5.0748</v>
       </c>
       <c r="E13" t="n">
-        <v>3.2498</v>
+        <v>2.7811</v>
       </c>
       <c r="F13" t="n">
-        <v>2.1663</v>
+        <v>2.2937</v>
       </c>
       <c r="G13" t="n">
         <v>1.583</v>
@@ -1468,13 +1468,13 @@
         <v>2.6433</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0833</v>
+        <v>-0.4245</v>
       </c>
       <c r="T13" t="n">
-        <v>0.08890000000000001</v>
+        <v>-0.3798</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1722</v>
+        <v>-0.0448</v>
       </c>
       <c r="V13" t="n">
         <v>1.4934</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.2597</v>
+        <v>3.6572</v>
       </c>
       <c r="E14" t="n">
-        <v>4.1001</v>
+        <v>3.5143</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1597</v>
+        <v>0.1429</v>
       </c>
       <c r="G14" t="n">
         <v>3.458</v>
@@ -1546,13 +1546,13 @@
         <v>1.3216</v>
       </c>
       <c r="S14" t="n">
-        <v>0.8017</v>
+        <v>0.1992</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9857</v>
+        <v>0.3999</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1839</v>
+        <v>-0.2007</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.1744</v>
+        <v>1.4817</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.1081</v>
+        <v>-0.9282</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2825</v>
+        <v>2.4099</v>
       </c>
       <c r="G15" t="n">
         <v>1.6922</v>
@@ -1624,13 +1624,13 @@
         <v>1.9825</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3854</v>
+        <v>-0.3074</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4732</v>
+        <v>-0.3469</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0878</v>
+        <v>0.0395</v>
       </c>
       <c r="V15" t="n">
         <v>-0.5639</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.6672</v>
+        <v>1.0442</v>
       </c>
       <c r="E16" t="n">
-        <v>3.1079</v>
+        <v>2.2878</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.4407</v>
+        <v>-1.2436</v>
       </c>
       <c r="G16" t="n">
         <v>2.6596</v>
@@ -1702,13 +1702,13 @@
         <v>0.2203</v>
       </c>
       <c r="S16" t="n">
-        <v>1.0604</v>
+        <v>0.4374</v>
       </c>
       <c r="T16" t="n">
-        <v>1.4341</v>
+        <v>0.6139</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3736</v>
+        <v>-0.1765</v>
       </c>
       <c r="V16" t="n">
         <v>-2.0528</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.261</v>
+        <v>0.7814</v>
       </c>
       <c r="E17" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.6519</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3271</v>
+        <v>0.1295</v>
       </c>
       <c r="G17" t="n">
         <v>4.1307</v>
@@ -1780,13 +1780,13 @@
         <v>0.8811</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.3739</v>
+        <v>-0.3316</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4484</v>
+        <v>0.1374</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.9255</v>
+        <v>-0.469</v>
       </c>
       <c r="V17" t="n">
         <v>-0.3745</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9075</v>
+        <v>-0.3133</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.989</v>
+        <v>-2.6375</v>
       </c>
       <c r="F18" t="n">
-        <v>2.0815</v>
+        <v>2.3242</v>
       </c>
       <c r="G18" t="n">
         <v>-0.2762</v>
@@ -1858,13 +1858,13 @@
         <v>1.7622</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0718</v>
+        <v>-0.4776</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5765</v>
+        <v>-0.225</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4953</v>
+        <v>-0.2526</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.2167</v>
+        <v>-1.2152</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.567</v>
+        <v>-1.9812</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3503</v>
+        <v>0.766</v>
       </c>
       <c r="G19" t="n">
         <v>-1.5274</v>
@@ -1936,13 +1936,13 @@
         <v>1.7622</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.469</v>
+        <v>-0.4675</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7046</v>
+        <v>-0.1188</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7644</v>
+        <v>-0.3487</v>
       </c>
       <c r="V19" t="n">
         <v>0.5595</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.3035</v>
+        <v>-3.5736</v>
       </c>
       <c r="E20" t="n">
-        <v>-5.4119</v>
+        <v>-4.8261</v>
       </c>
       <c r="F20" t="n">
-        <v>1.1084</v>
+        <v>1.2525</v>
       </c>
       <c r="G20" t="n">
         <v>-0.5798</v>
@@ -2014,13 +2014,13 @@
         <v>2.6433</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.3537</v>
+        <v>-0.6237</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.2811</v>
+        <v>-0.6953</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0726</v>
+        <v>0.0716</v>
       </c>
       <c r="V20" t="n">
         <v>-1.4889</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.4268</v>
+        <v>-3.9731</v>
       </c>
       <c r="E21" t="n">
-        <v>-6.2073</v>
+        <v>-5.6214</v>
       </c>
       <c r="F21" t="n">
-        <v>1.7804</v>
+        <v>1.6484</v>
       </c>
       <c r="G21" t="n">
         <v>-0.6561</v>
@@ -2092,13 +2092,13 @@
         <v>2.2027</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8013</v>
+        <v>-0.3476</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.4092</v>
+        <v>-0.8234</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6079</v>
+        <v>0.4758</v>
       </c>
       <c r="V21" t="n">
         <v>0.555</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.401899999999999</v>
+        <v>2.964099999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>-6.759399999999999</v>
+        <v>-6.759300000000002</v>
       </c>
       <c r="F22" t="n">
-        <v>8.161300000000001</v>
+        <v>9.7235</v>
       </c>
       <c r="G22" t="n">
         <v>10.484</v>
@@ -2170,13 +2170,13 @@
         <v>15.4192</v>
       </c>
       <c r="S22" t="n">
-        <v>-3.9055</v>
+        <v>-2.3433</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.4379</v>
+        <v>-1.438</v>
       </c>
       <c r="U22" t="n">
-        <v>-2.4674</v>
+        <v>-0.9054</v>
       </c>
       <c r="V22" t="n">
         <v>-1.872199999999999</v>
